--- a/Outputs/Scenarios/PtX_demand_LT_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LT_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.003207264563663378</v>
       </c>
       <c r="K16" t="n">
-        <v>0.003817961246234319</v>
+        <v>0.002073255167090504</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001272653748744773</v>
+        <v>0.003003009503643353</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>4.62112533740057e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001272653748744773</v>
+        <v>0.001287004072990009</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.004747964713591852</v>
       </c>
       <c r="K30" t="n">
-        <v>0.02060435491132469</v>
+        <v>0.01118871631465711</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.006868118303774898</v>
+        <v>0.01620631264295216</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0002498928796627291</v>
       </c>
       <c r="K42" t="n">
-        <v>0.006868118303774898</v>
+        <v>0.006945562561265214</v>
       </c>
     </row>
     <row r="43">
